--- a/S2_quantum_resource_audit.xlsx
+++ b/S2_quantum_resource_audit.xlsx
@@ -634,7 +634,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>[73]</t>
+          <t>[93]</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>[74]</t>
+          <t>[94]</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>[75]</t>
+          <t>[95]</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>[76]</t>
+          <t>[96]</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>[77]</t>
+          <t>[97]</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>[78]</t>
+          <t>[98]</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[99]</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>[80]</t>
+          <t>[84]</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1062,7 +1062,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>[81]</t>
+          <t>[85]</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>[82]</t>
+          <t>[100]</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>[83]</t>
+          <t>[101]</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>[84]</t>
+          <t>[50]</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>[85]</t>
+          <t>[102]</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>[86]</t>
+          <t>[103]</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>[87]</t>
+          <t>[104]</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>[88]</t>
+          <t>[105]</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>[89]</t>
+          <t>[106]</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>[90]</t>
+          <t>[107]</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1600,7 +1600,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>[91]</t>
+          <t>[108]</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>[92]</t>
+          <t>[109]</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1706,7 +1706,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>[93]</t>
+          <t>[42]</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>[94]</t>
+          <t>[43]</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>[95]</t>
+          <t>[44]</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>[96]</t>
+          <t>[45]</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1922,7 +1922,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>[97]</t>
+          <t>[46]</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>[98]</t>
+          <t>[110]</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2032,7 +2032,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>[99]</t>
+          <t>[52]</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>[104]</t>
+          <t>[115]</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>[105]</t>
+          <t>[116]</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>[106]</t>
+          <t>[117]</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>[107]</t>
+          <t>[118]</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>[108]</t>
+          <t>[119]</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2366,7 +2366,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>[109]</t>
+          <t>[86]</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>[110]</t>
+          <t>[87]</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2480,7 +2480,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>[111]</t>
+          <t>[48]</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2533,7 +2533,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>[112]</t>
+          <t>[49]</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>[113]</t>
+          <t>[120]</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>[114]</t>
+          <t>[121]</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2700,7 +2700,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>[115]</t>
+          <t>[47]</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2757,7 +2757,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>[116]</t>
+          <t>[88]</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>[117]</t>
+          <t>[89]</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2871,7 +2871,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>[118]</t>
+          <t>[51]</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>[126]</t>
+          <t>[90]</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2985,7 +2985,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>[122]</t>
+          <t>[91]</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>[134]</t>
+          <t>[38]</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>[135]</t>
+          <t>[39]</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3360,7 +3360,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>[117]</t>
+          <t>[89]</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3513,7 +3513,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>[110]</t>
+          <t>[87]</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>[122]</t>
+          <t>[91]</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3815,7 +3815,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>[116]</t>
+          <t>[88]</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3972,7 +3972,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>[109]</t>
+          <t>[86]</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>[126]</t>
+          <t>[90]</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4272,7 +4272,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>[81]</t>
+          <t>[85]</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4423,7 +4423,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>[80]</t>
+          <t>[84]</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4576,7 +4576,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>[113]</t>
+          <t>[120]</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4663,7 +4663,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>[114]</t>
+          <t>[121]</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>[105]</t>
+          <t>[116]</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -4839,7 +4839,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>[73]</t>
+          <t>[93]</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>[74]</t>
+          <t>[94]</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>[75]</t>
+          <t>[95]</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>[76]</t>
+          <t>[96]</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5157,7 +5157,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>[77]</t>
+          <t>[97]</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>[78]</t>
+          <t>[98]</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[99]</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5428,7 +5428,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>[88]</t>
+          <t>[105]</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>[89]</t>
+          <t>[106]</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -5612,7 +5612,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>[90]</t>
+          <t>[107]</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>[91]</t>
+          <t>[108]</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5788,7 +5788,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>[92]</t>
+          <t>[109]</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5875,7 +5875,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>[82]</t>
+          <t>[100]</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5956,7 +5956,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>[83]</t>
+          <t>[101]</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>[85]</t>
+          <t>[102]</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6092,7 +6092,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>[86]</t>
+          <t>[103]</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6181,7 +6181,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>[87]</t>
+          <t>[104]</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6274,7 +6274,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>[98]</t>
+          <t>[110]</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6361,7 +6361,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>[104]</t>
+          <t>[115]</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>[106]</t>
+          <t>[117]</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -6545,7 +6545,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>[107]</t>
+          <t>[118]</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6634,7 +6634,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>[108]</t>
+          <t>[119]</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6725,7 +6725,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>[134]</t>
+          <t>[38]</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6849,12 +6849,16 @@
           <t>Full text: system model, QRL algorithm, Table I, simulation results</t>
         </is>
       </c>
-      <c r="AE35" s="3" t="n"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Secrecy maximization for pico edge users: a quantum RL approach</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>[135]</t>
+          <t>[39]</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -6978,7 +6982,11 @@
           <t>Full text: problem formulation, Algorithm 1, simulation setup, Fig. 6</t>
         </is>
       </c>
-      <c r="AE36" s="3" t="n"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Secure quantum federated learning for URLLC in 6G smart healthcare</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
